--- a/elenco_tecnici.xlsx
+++ b/elenco_tecnici.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\DOC - Manuela Arigoni\SW FERIE CLIENTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB34AD01-4AD6-49AF-94BB-9082BC9DA632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F499215-4DEF-42E2-A502-6BBDCEA729F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22545" yWindow="4290" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TECNICI" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>EMAIL</t>
   </si>
@@ -123,6 +123,15 @@
   </si>
   <si>
     <t>WinRicky2026</t>
+  </si>
+  <si>
+    <t>Adriano Giannelavigna</t>
+  </si>
+  <si>
+    <t>adriano.giannelavigna@wingaming.it</t>
+  </si>
+  <si>
+    <t>WinAdri2026</t>
   </si>
 </sst>
 </file>
@@ -169,7 +178,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -192,16 +201,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -517,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56295C2E-C6A6-445F-99D3-BA76E299DEF4}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -622,6 +645,17 @@
       </c>
       <c r="C9" s="3" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -635,6 +669,7 @@
     <hyperlink ref="B2" r:id="rId6" xr:uid="{7327F9ED-3DE1-420C-95C5-F4752F415793}"/>
     <hyperlink ref="B4" r:id="rId7" xr:uid="{A2FB9C8F-D68C-4361-8EE9-2F87DF12FC28}"/>
     <hyperlink ref="B9" r:id="rId8" xr:uid="{1673C42C-99AA-4CAA-B432-0B487EF9C761}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{C0D225AA-2C6D-48FE-9A33-D79620D3B330}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/elenco_tecnici.xlsx
+++ b/elenco_tecnici.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\DOC - Manuela Arigoni\SW FERIE CLIENTI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\DOC - Manuela Arigoni\SW PERSONALIZZATI\SW FERIE CLIENTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F499215-4DEF-42E2-A502-6BBDCEA729F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47520A4A-037D-40A3-9AE8-DCCBF13D4E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24735" yWindow="3735" windowWidth="15375" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TECNICI" sheetId="3" r:id="rId1"/>
@@ -95,9 +95,6 @@
     <t>saverio.bianco@wingaming.it</t>
   </si>
   <si>
-    <t>rtatiana.vinogradova@wingaming.it</t>
-  </si>
-  <si>
     <t>PASSWORD</t>
   </si>
   <si>
@@ -132,6 +129,9 @@
   </si>
   <si>
     <t>WinAdri2026</t>
+  </si>
+  <si>
+    <t>tatiana.vinogradova@wingaming.it</t>
   </si>
 </sst>
 </file>
@@ -217,14 +217,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -556,7 +557,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -567,7 +568,7 @@
         <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -578,7 +579,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -589,7 +590,7 @@
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -600,7 +601,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -611,7 +612,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -622,7 +623,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -633,29 +634,29 @@
         <v>9</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
+      <c r="B9" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/elenco_tecnici.xlsx
+++ b/elenco_tecnici.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\DOC - Manuela Arigoni\SW PERSONALIZZATI\SW FERIE CLIENTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47520A4A-037D-40A3-9AE8-DCCBF13D4E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ADFE30E-D9EE-4AB2-AEE1-AE04D567E233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24735" yWindow="3735" windowWidth="15375" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="3225" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TECNICI" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TECNICI!$A$1:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TECNICI!$A$1:$D$11</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>EMAIL</t>
   </si>
@@ -132,6 +132,24 @@
   </si>
   <si>
     <t>tatiana.vinogradova@wingaming.it</t>
+  </si>
+  <si>
+    <t>RUOLO</t>
+  </si>
+  <si>
+    <t>tecnico</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>Alessandro Frigerio</t>
+  </si>
+  <si>
+    <t>alessandro.frigerio@wingaming.it</t>
+  </si>
+  <si>
+    <t>WinAle2026</t>
   </si>
 </sst>
 </file>
@@ -178,7 +196,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -201,31 +219,19 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -541,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56295C2E-C6A6-445F-99D3-BA76E299DEF4}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -549,7 +555,7 @@
     <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -559,8 +565,11 @@
       <c r="C1" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -570,8 +579,11 @@
       <c r="C2" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -581,8 +593,11 @@
       <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -592,8 +607,11 @@
       <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -603,8 +621,11 @@
       <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -614,8 +635,11 @@
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -625,8 +649,11 @@
       <c r="C7" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
@@ -636,31 +663,54 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="D9" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="D10" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C9" xr:uid="{56295C2E-C6A6-445F-99D3-BA76E299DEF4}"/>
+  <autoFilter ref="A1:D11" xr:uid="{56295C2E-C6A6-445F-99D3-BA76E299DEF4}"/>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{BA7E3E07-04A7-4A82-A601-E295B1CEE7C1}"/>
     <hyperlink ref="B7" r:id="rId2" xr:uid="{674147B8-D281-4466-9000-74594D6F788F}"/>
@@ -671,6 +721,7 @@
     <hyperlink ref="B4" r:id="rId7" xr:uid="{A2FB9C8F-D68C-4361-8EE9-2F87DF12FC28}"/>
     <hyperlink ref="B9" r:id="rId8" xr:uid="{1673C42C-99AA-4CAA-B432-0B487EF9C761}"/>
     <hyperlink ref="B10" r:id="rId9" xr:uid="{C0D225AA-2C6D-48FE-9A33-D79620D3B330}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{7C9ECE65-2AAC-4A18-9316-CD5B131DAB66}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
